--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_論点漏れの点検_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_論点漏れの点検_20261020.xlsx
@@ -647,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">

--- a/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_論点漏れの点検_20261020.xlsx
+++ b/小野町_引継ぎ_整理済/03_計画素案/小野町_障がい計画_論点漏れの点検_20261020.xlsx
@@ -1155,7 +1155,7 @@
         <v>11</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17">
